--- a/AAII_Financials/Quarterly/UBER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UBER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>UBER</t>
   </si>
@@ -656,460 +656,473 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="31" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="32" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14191000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13203000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14366000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13467000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12651000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11533000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11959000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11188000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10700000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10131000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9936000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9292000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9230000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8823000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8607000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8343000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8073000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6854000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5778000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4845000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3929000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2903000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3165000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2813000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1913000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3248000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2922000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3813000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3166000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3099000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3006000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2973000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5388000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2584000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2441000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8620000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8021000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7236000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8844000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8307000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7605000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6012000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7448000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7170000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6853000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6759000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6309000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6179000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5899000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5912000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5790000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5770000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4600000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3651000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2913000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2531000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2133000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1820000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1663000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1506000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1994000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1286000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2358000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2604000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2115000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2023000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1897000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3219000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1528000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1566000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5571000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5182000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7130000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4623000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4344000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3928000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5947000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3740000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3530000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3278000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3177000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2983000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3051000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2924000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2695000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2553000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2303000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2254000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2127000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1932000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1398000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>770000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1345000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1150000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>407000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1254000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1636000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1455000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>562000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>984000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>983000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1076000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2169000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1056000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>875000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1147,115 +1160,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1043000</v>
+      </c>
+      <c r="E12" s="3">
         <v>951000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>885000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>862000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>840000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>815000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>785000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>774000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>760000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>790000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>784000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>797000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>808000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>775000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>747000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>760000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>704000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>587000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>558000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>493000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>488000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>515000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>484000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>493000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>584000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>645000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>608000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>755000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3064000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>409000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>366000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>434000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>705000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>340000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>320000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,65 +1378,68 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-1612000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1474000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1602000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1471000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>17000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-51000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-320000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1664000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-333000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>721000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1640000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>96000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-312000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-320000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-14000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>182000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1427,156 +1447,162 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-1684000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-90000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>239000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>412000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1902000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-444000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>26000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>22000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-3165000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-3161000</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E15" s="3">
         <v>184000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>185000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>188000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>175000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>171000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>169000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>179000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>173000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>190000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>203000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>205000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>208000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>207000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>223000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>227000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>243000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>254000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>246000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>218000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>226000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>212000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>180000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>138000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>129000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>128000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>101000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>102000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>123000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>146000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>109000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>131000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>186000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>88000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1611,222 +1637,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12301000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11280000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12592000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12354000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11201000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10305000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11189000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10127000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9904000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9959000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9284000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8898000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8904000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9085000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8749000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8824000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8786000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7518000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6328000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5417000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5117000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2743000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3965000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3769000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3534000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6220000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3893000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4919000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8207000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4133000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4053000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3729000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3404000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>-99000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3638000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1890000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1923000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1774000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1113000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1450000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1228000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>770000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1061000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>796000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>172000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>652000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>394000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>326000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-262000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-142000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-481000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-713000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-664000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-550000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-572000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1188000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>160000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-800000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-956000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1621000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2972000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-971000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1106000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5041000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1034000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1047000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-756000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1984000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2683000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-1197000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1864,543 +1897,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E20" s="3">
         <v>40000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-20000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>59000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-29000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>265000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>20000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>101000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>120000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>464000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>83000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>142000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>79000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>767000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-549000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1704000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5375000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1471000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1832000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1943000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>26000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>331000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-86000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>15000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>49000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-46000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>260000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>41000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-61000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1799000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1776000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1787000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2067000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1979000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1242000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1611000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1428000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>674000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1220000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>868000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>242000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>391000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>516000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>392000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-134000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>848000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-803000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2174000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5785000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1167000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2186000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>981000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>398000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-634000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-487000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1522000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2930000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-855000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-955000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4964000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-628000</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-686000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3969000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4547000</v>
       </c>
-      <c r="AK21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E22" s="3">
         <v>108000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>115000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>112000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>108000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>105000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>117000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>143000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>139000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>124000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>155000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>166000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>144000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>168000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>151000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>146000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>139000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>129000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>130000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>123000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>115000</v>
       </c>
       <c r="X22" s="3">
         <v>115000</v>
       </c>
       <c r="Y22" s="3">
+        <v>115000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>118000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>452000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>110000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>118000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>101000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>90000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>151000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>217000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>195000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>161000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>292000</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>132000</v>
       </c>
       <c r="AK22" s="3">
         <v>132000</v>
       </c>
+      <c r="AL22" s="3">
+        <v>132000</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3256000</v>
+      </c>
+      <c r="E23" s="3">
         <v>476000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>277000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2606000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1492000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1372000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>899000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2757000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1065000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-634000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1833000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>179000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>459000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-102000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>474000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1176000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2556000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6168000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>791000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2527000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>640000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>71000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-932000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1761000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3176000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1057000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1147000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5238000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-991000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1201000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-978000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3491000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4327000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1298000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E24" s="3">
         <v>194000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-40000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4046000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>142000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-402000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-6002000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>158000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>57000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>133000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-40000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>65000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>55000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-84000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>58000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>77000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-232000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-97000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-101000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-479000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>185000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>23000</v>
       </c>
       <c r="Z24" s="3">
         <v>23000</v>
       </c>
       <c r="AA24" s="3">
+        <v>23000</v>
+      </c>
+      <c r="AB24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-242000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>25000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>19000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-322000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>604000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>576000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>67000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2506,222 +2555,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="E26" s="3">
         <v>282000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>317000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6652000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1350000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1774000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6901000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2599000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1008000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-663000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1700000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>219000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>394000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>558000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1234000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2633000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5936000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>888000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2426000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1119000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-114000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-955000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1100000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1765000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2934000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1082000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1150000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5236000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1010000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-879000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-979000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2887000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3751000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1365000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="E27" s="3">
         <v>263000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>296000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6626000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1355000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1776000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6883000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2612000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1015000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-654000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1429000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>221000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>394000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>595000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1206000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2601000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5930000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>892000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2424000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1144000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-108000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-967000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1091000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1775000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2936000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1096000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1162000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5236000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1012000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-260000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-986000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1246000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1462000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1365000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2827,8 +2885,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2913,14 +2974,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
@@ -2932,10 +2993,13 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>722000</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3041,8 +3105,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3148,222 +3215,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-291000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-40000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>20000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-59000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>29000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-265000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-20000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-101000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-120000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-464000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-83000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-142000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-767000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>549000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1704000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5375000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1471000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1832000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1943000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>14000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-331000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>30000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>86000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>46000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-260000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>61000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1799000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1776000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="E33" s="3">
         <v>263000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>296000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6626000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1355000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1776000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6883000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2612000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1015000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-654000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1429000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>221000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>394000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>595000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1206000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2601000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5930000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>892000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2424000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1144000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-108000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-967000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1091000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1775000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2936000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1096000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1162000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5236000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1012000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-260000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-986000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1246000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1462000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-643000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3469,227 +3545,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="E35" s="3">
         <v>263000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>296000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6626000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1355000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1776000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6883000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2612000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1015000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-654000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1429000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>221000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>394000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>595000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1206000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2601000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5930000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>892000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2424000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1144000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-108000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-967000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1091000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1775000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2936000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1096000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1162000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5236000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1012000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-260000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-986000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1246000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1462000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-643000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3727,8 +3812,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3766,101 +3852,102 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4870000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5558000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7105000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8432000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6438000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5132000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5893000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6150000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4497000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5019000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4680000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4448000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4995000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4045000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4208000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4865000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4397000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4184000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4295000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6482000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4443000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4836000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5647000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6154000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6754000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8165000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10873000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12650000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11744000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5745000</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3873,92 +3960,95 @@
       <c r="AK41" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>521000</v>
+      </c>
+      <c r="E42" s="3">
         <v>533000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>528000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>654000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>932000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>894000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1084000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2913000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1795000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>744000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>727000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>725000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>538000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>121000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>103000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>10</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>560000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>819000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1180000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1132000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1033000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>831000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>440000</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3971,8 +4061,8 @@
       <c r="AH42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI42" s="3">
-        <v>0</v>
+      <c r="AI42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AJ42" s="3">
         <v>0</v>
@@ -3980,101 +4070,104 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4298000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3895000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3827000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3773000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4406000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4001000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3333000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4187000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4372000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4462000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4121000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3669000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3235000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3281000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3489000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3092000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3074000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3091000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2992000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1927000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1734000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1617000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1537000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1139000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1037000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1169000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1642000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1735000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1874000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1557000</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>10</v>
       </c>
@@ -4087,8 +4180,11 @@
       <c r="AK43" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4131,8 +4227,8 @@
       <c r="P44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4194,101 +4290,104 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1769000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1663000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1494000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1355000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>717000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>615000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>975000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>681000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>679000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>675000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>564000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>580000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>634000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>492000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1449000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1411000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1280000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1390000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1532000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1275000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1046000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1023000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1518000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>987000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>838000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>949000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>970000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>768000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>682000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>628000</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>10</v>
       </c>
@@ -4301,101 +4400,104 @@
       <c r="AK45" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12529000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12823000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13993000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15139000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14107000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12350000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12245000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15331000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12483000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12074000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11297000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10679000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10664000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9196000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9249000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9368000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8751000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8665000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8819000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9684000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7783000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8295000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9882000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9412000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9662000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11114000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13925000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15153000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14300000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7930000</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>10</v>
       </c>
@@ -4408,101 +4510,104 @@
       <c r="AK46" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12532000</v>
+      </c>
+      <c r="E47" s="3">
         <v>8377000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9465000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10645000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8991000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9084000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8762000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8235000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6545000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5941000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6454000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5141000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5167000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5458000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6885000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4545000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5093000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6871000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12606000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13210000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>14871000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12921000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>10131000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>10173000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>9875000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>9986000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>11891000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>11805000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>11785000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>11716000</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>10</v>
       </c>
@@ -4515,101 +4620,104 @@
       <c r="AK47" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3367000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3011000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3056000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3101000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3103000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3110000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3172000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3215000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3249000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3314000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3359000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3411000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3477000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3531000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3347000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3342000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3292000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3241000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2999000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3014000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3024000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3088000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3210000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3287000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3440000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3325000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3075000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2784000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2648000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>10</v>
       </c>
@@ -4622,101 +4730,104 @@
       <c r="AK48" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10604000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9909000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9979000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10021000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10094000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9134000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9191000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9278000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9348000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9424000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9576000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9651000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9758000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9951000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10137000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10292000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10481000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10704000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10832000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7725000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7826000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7807000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7673000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3642000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3051000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3126000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>238000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>241000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>245000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>231000</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>10</v>
       </c>
@@ -4729,8 +4840,11 @@
       <c r="AK49" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4836,8 +4950,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4943,101 +5060,104 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16165000</v>
+      </c>
+      <c r="E52" s="3">
         <v>14210000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14019000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13391000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12785000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12206000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11477000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10794000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9648000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8633000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7888000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6879000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4819000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4122000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2307000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3560000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3347000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3280000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3276000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3266000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2757000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2608000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2478000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2457000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2365000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2424000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2382000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2018000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1866000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1865000</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>10</v>
       </c>
@@ -5050,8 +5170,11 @@
       <c r="AK52" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5157,101 +5280,104 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>65801000</v>
+      </c>
+      <c r="E54" s="3">
         <v>59885000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>61802000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>63344000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>55982000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>52822000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51244000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>47117000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>41514000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39599000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>38699000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35949000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34068000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32451000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32109000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31112000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31014000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32812000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38774000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>36884000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>36251000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34655000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33252000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28894000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28240000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30090000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>31761000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>32292000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30980000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24390000</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>10</v>
       </c>
@@ -5264,8 +5390,11 @@
       <c r="AK54" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5303,8 +5432,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5342,101 +5472,102 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1366000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1189000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1013000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1119000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1022000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>873000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>858000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>802000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>752000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>833000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>790000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>799000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>694000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>712000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>728000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>774000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>810000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>862000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>860000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>310000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>429000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>232000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>235000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>240000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>253000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>215000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>272000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>126000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>167000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>151000</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>10</v>
       </c>
@@ -5449,61 +5580,64 @@
       <c r="AK57" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2175000</v>
+      </c>
+      <c r="E58" s="3">
         <v>195000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>307000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1313000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1326000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1327000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1461000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>806000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>351000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>337000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>371000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>327000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>332000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>370000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>10</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5514,36 +5648,36 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z58" s="3">
         <v>525000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>708000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>193000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1085000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>165000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>130000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>133000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>115000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>10</v>
       </c>
@@ -5556,101 +5690,104 @@
       <c r="AK58" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3385000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3300000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3158000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3183000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2984000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3059000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2800000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2635000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2630000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2525000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2466000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2437000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2459000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2476000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8125000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8246000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8135000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7790000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8164000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7816000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7255000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7056000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6105000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5973000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5445000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5331000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5202000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5116000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5270000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4448000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>10</v>
       </c>
@@ -5663,101 +5800,104 @@
       <c r="AK59" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14871000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11993000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12320000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13121000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12686000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12113000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11476000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10835000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10318000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9993000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9454000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9405000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8635000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8683000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8853000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9020000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8945000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8652000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9024000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8126000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7684000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7288000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6865000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6921000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5891000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6631000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5639000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5372000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5570000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4714000</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>10</v>
       </c>
@@ -5770,101 +5910,104 @@
       <c r="AK60" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12556000</v>
+      </c>
+      <c r="E61" s="3">
         <v>12224000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11995000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12027000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11016000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9797000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9975000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12482000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10946000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10977000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11331000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10817000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10852000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10886000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9265000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9268000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9271000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9273000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9276000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9279000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7798000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7801000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7680000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6743000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6768000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5781000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5928000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5934000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4755000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7157000</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -5877,101 +6020,104 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9949000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9828000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9373000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9010000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8582000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7994000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7308000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7106000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6432000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6092000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5176000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5126000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4702000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4178000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5487000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5424000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5235000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5069000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5125000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5194000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5025000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5495000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4953000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5048000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5060000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5360000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5011000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4935000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4747000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6731000</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5984,8 +6130,11 @@
       <c r="AK62" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6091,8 +6240,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6198,8 +6350,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6305,101 +6460,104 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37402000</v>
+      </c>
+      <c r="E66" s="3">
         <v>34073000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33719000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>34189000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32352000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29917000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28768000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30578000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27731000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27100000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26017000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25430000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24240000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23779000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>24769000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>24865000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>24353000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23896000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>24316000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22953000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22076000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21057000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20986000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19952000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18690000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18748000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17571000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17230000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15058000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>18598000</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>10</v>
       </c>
@@ -6412,8 +6570,11 @@
       <c r="AK66" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6451,8 +6612,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6558,8 +6720,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6665,8 +6830,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6755,11 +6923,11 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>14224000</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
@@ -6772,8 +6940,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6879,101 +7050,104 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7950000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10355000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10628000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10935000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-17592000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-18946000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-20726000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-27621000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-30233000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-31248000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-30594000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-32309000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-32530000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-32924000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-32767000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-33363000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-32157000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-29556000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-23626000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-24518000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-22094000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-23238000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-23130000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-22162000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-21073000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-19298000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-16362000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-15266000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-14104000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-8868000</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>10</v>
       </c>
@@ -6986,8 +7160,11 @@
       <c r="AK72" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7093,8 +7270,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7200,8 +7380,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7307,101 +7490,104 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27316000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24751000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>27041000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>28134000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22598000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21975000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21558000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14780000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12350000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11058000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11249000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9358000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8664000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7508000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7340000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6247000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6661000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8916000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14458000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13931000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14175000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13598000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12266000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8942000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9550000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11342000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14190000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15062000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15922000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-8432000</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>10</v>
       </c>
@@ -7414,8 +7600,11 @@
       <c r="AK76" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7521,227 +7710,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="E81" s="3">
         <v>263000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>296000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6626000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1355000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1776000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6883000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2612000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1015000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-654000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1429000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>221000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>394000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>595000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1206000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2601000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5930000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>892000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2424000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1144000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-108000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-967000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1091000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1775000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2936000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1096000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1162000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5236000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1012000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-260000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-986000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1246000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1462000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-643000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7779,115 +7977,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E83" s="3">
         <v>114000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>110000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>186000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>181000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>194000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>115000</v>
       </c>
       <c r="J83" s="3">
         <v>115000</v>
       </c>
       <c r="K83" s="3">
+        <v>115000</v>
+      </c>
+      <c r="L83" s="3">
         <v>118000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>113000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>109000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>101000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>104000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>110000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>223000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>227000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>243000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>254000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>246000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>218000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>226000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>212000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>180000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>138000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>129000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>128000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>101000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>102000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>123000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>146000</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI83" s="3">
         <v>131000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>186000</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK83" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7993,8 +8195,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8100,8 +8305,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8207,8 +8415,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8314,8 +8525,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8421,115 +8635,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2862000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2351000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2883000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2328000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2564000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2324000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1750000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2151000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1820000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1416000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>823000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>966000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1190000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>606000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-244000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>432000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>439000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>15000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-107000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>614000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-341000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-262000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1154000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-406000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1071000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-463000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1799000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-878000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-922000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-688000</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-350000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-456000</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK89" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8567,115 +8787,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-65000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-75000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-98000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-89000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-74000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-44000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-99000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-57000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-55000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-61000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-50000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-57000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-59000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-74000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-57000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-62000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-80000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-90000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-57000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-71000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-123000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-131000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-164000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-198000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-182000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-129000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-148000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-129000</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-153000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-209000</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK91" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8781,8 +9005,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8888,115 +9115,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5389000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-773000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1614000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>53000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1461000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-542000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1433000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2692000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1676000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-242000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-819000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2416000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>408000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-399000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1769000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>321000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-54000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-135000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2268000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1216000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>101000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-250000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-192000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-365000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-456000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1856000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-711000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-129000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-154000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>204000</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-73000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-466000</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK94" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9034,8 +9267,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9078,8 +9312,8 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -9141,8 +9375,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9248,8 +9485,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9355,8 +9595,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9462,325 +9705,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1540000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3091000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3118000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-538000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-195000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1862000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3397000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1601000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-191000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>46000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-76000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>42000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-107000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-89000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>212000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-113000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>414000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1556000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>36000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-226000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>896000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>428000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>118000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-63000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-83000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1993000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>7075000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-46000</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-313000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2476000</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK100" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E101" s="3">
         <v>70000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-179000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>62000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-56000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-94000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>89000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-69000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>27000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>16000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>145000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-195000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-118000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>20000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>145000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-195000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-118000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>20000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-24000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-50000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>51000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-46000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>75000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-156000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>19000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-35000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>9000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3000</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AH101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-31000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-102000</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK101" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL101" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-933000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1537000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1836000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1816000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1067000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-393000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1122000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-103000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>980000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>139000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1595000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1667000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>116000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1957000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>770000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>272000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-213000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1985000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3336000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-153000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-784000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-375000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-335000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1428000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2538000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2574000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>951000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6008000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-527000</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-767000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1452000</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AK102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>10</v>
       </c>
     </row>
